--- a/CE国試data/CE_questions_2015.xlsx
+++ b/CE国試data/CE_questions_2015.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
